--- a/output/2026-09-09_盤中掃描_低波幅20分鐘均線.xlsx
+++ b/output/2026-09-09_盤中掃描_低波幅20分鐘均線.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_板塊資金流" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_今日背景與時間表" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_限制與來源" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TV_連結" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +23,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="+0.00%;-0.00%"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -83,8 +84,23 @@
       <color rgb="009C0006"/>
       <sz val="10"/>
     </font>
+    <font>
+      <color rgb="000563C1"/>
+      <sz val="10"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="000563C1"/>
+      <sz val="10"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <color rgb="00595959"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -129,6 +145,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F5FB"/>
       </patternFill>
     </fill>
   </fills>
@@ -202,7 +223,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -270,6 +291,72 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -350,7 +437,6 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="11"/>
   <chart>
     <title>
       <tx>
@@ -769,6 +855,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="26" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -782,22 +869,22 @@
           <t>指數</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="25" t="inlineStr">
         <is>
           <t>S&amp;P 500</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="25" t="inlineStr">
         <is>
           <t>道指</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="25" t="inlineStr">
         <is>
           <t>納指</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="25" t="inlineStr">
         <is>
           <t>羅素2000</t>
         </is>
@@ -840,6 +927,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="26" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
@@ -883,7 +971,7 @@
       <c r="A10" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="26" t="inlineStr">
         <is>
           <t>XOM</t>
         </is>
@@ -916,7 +1004,7 @@
       <c r="A11" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="26" t="inlineStr">
         <is>
           <t>CVX</t>
         </is>
@@ -946,12 +1034,12 @@
       <c r="A12" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="26" t="inlineStr">
         <is>
           <t>AVGO</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="26" t="inlineStr">
         <is>
           <t>隨 SMH 走強</t>
         </is>
@@ -977,12 +1065,12 @@
       <c r="A13" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="26" t="inlineStr">
         <is>
           <t>NVDA</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C13" s="26" t="inlineStr">
         <is>
           <t>隨 SMH 走強</t>
         </is>
@@ -1008,7 +1096,7 @@
       <c r="A14" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="26" t="inlineStr">
         <is>
           <t>XLU 成分</t>
         </is>
@@ -1035,6 +1123,7 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
@@ -1063,7 +1152,7 @@
       </c>
     </row>
     <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="12" t="inlineStr">
+      <c r="A18" s="27" t="inlineStr">
         <is>
           <t>AAPL</t>
         </is>
@@ -1083,7 +1172,7 @@
       </c>
     </row>
     <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="12" t="inlineStr">
+      <c r="A19" s="27" t="inlineStr">
         <is>
           <t>META</t>
         </is>
@@ -1103,7 +1192,7 @@
       </c>
     </row>
     <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="12" t="inlineStr">
+      <c r="A20" s="27" t="inlineStr">
         <is>
           <t>VLO / 煉油股</t>
         </is>
@@ -1136,14 +1225,14 @@
       <c r="C21" s="13" t="inlineStr"/>
       <c r="D21" s="13" t="inlineStr"/>
       <c r="E21" s="13" t="inlineStr"/>
-      <c r="F21" s="14" t="inlineStr">
+      <c r="F21" s="28" t="inlineStr">
         <is>
           <t>同上，日內振幅通常是 XOM 的 2 倍</t>
         </is>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1">
-      <c r="A22" s="12" t="inlineStr">
+      <c r="A22" s="27" t="inlineStr">
         <is>
           <t>DAL / 運輸股</t>
         </is>
@@ -1163,7 +1252,7 @@
       </c>
     </row>
     <row r="23" ht="24" customHeight="1">
-      <c r="A23" s="12" t="inlineStr">
+      <c r="A23" s="27" t="inlineStr">
         <is>
           <t>XLV 成分</t>
         </is>
@@ -1183,7 +1272,7 @@
       </c>
     </row>
     <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="12" t="inlineStr">
+      <c r="A24" s="27" t="inlineStr">
         <is>
           <t>XLF 成分</t>
         </is>
@@ -1222,6 +1311,7 @@
         </is>
       </c>
     </row>
+    <row r="26"/>
     <row r="27" ht="26" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
@@ -1243,6 +1333,7 @@
       <c r="E28" s="16" t="n"/>
       <c r="F28" s="17" t="n"/>
     </row>
+    <row r="29"/>
     <row r="30" ht="26" customHeight="1">
       <c r="A30" s="18" t="inlineStr">
         <is>
@@ -1276,6 +1367,26 @@
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A30:F30"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A24" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1302,6 +1413,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="32" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
@@ -1325,7 +1437,7 @@
       </c>
     </row>
     <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="35" t="inlineStr">
         <is>
           <t>SMH 半導體</t>
         </is>
@@ -1345,7 +1457,7 @@
       </c>
     </row>
     <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="35" t="inlineStr">
         <is>
           <t>XLE 能源</t>
         </is>
@@ -1365,7 +1477,7 @@
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="35" t="inlineStr">
         <is>
           <t>XLU 公用</t>
         </is>
@@ -1385,7 +1497,7 @@
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="35" t="inlineStr">
         <is>
           <t>XLV 醫療</t>
         </is>
@@ -1405,7 +1517,7 @@
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="35" t="inlineStr">
         <is>
           <t>XLF 金融</t>
         </is>
@@ -1428,8 +1540,15 @@
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
 </worksheet>
 </file>
 
@@ -1453,6 +1572,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="53" customHeight="1">
       <c r="A3" s="23" t="inlineStr">
         <is>
@@ -1527,6 +1647,7 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10" ht="26" customHeight="1">
       <c r="A10" s="1" t="inlineStr">
         <is>
@@ -1547,7 +1668,7 @@
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="24" t="inlineStr">
+      <c r="A12" s="33" t="inlineStr">
         <is>
           <t>11:12</t>
         </is>
@@ -1559,7 +1680,7 @@
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="24" t="inlineStr">
+      <c r="A13" s="33" t="inlineStr">
         <is>
           <t>11:30–13:00</t>
         </is>
@@ -1571,7 +1692,7 @@
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="24" t="inlineStr">
+      <c r="A14" s="33" t="inlineStr">
         <is>
           <t>13:00</t>
         </is>
@@ -1583,7 +1704,7 @@
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="24" t="inlineStr">
+      <c r="A15" s="33" t="inlineStr">
         <is>
           <t>13:05–14:00</t>
         </is>
@@ -1595,7 +1716,7 @@
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="24" t="inlineStr">
+      <c r="A16" s="33" t="inlineStr">
         <is>
           <t>約 13:00 起</t>
         </is>
@@ -1607,7 +1728,7 @@
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="24" t="inlineStr">
+      <c r="A17" s="33" t="inlineStr">
         <is>
           <t>15:00–16:00</t>
         </is>
@@ -1619,7 +1740,7 @@
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="24" t="inlineStr">
+      <c r="A18" s="33" t="inlineStr">
         <is>
           <t>盤後 / 隔夜</t>
         </is>
@@ -1659,6 +1780,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="84" customHeight="1">
       <c r="A3" s="23" t="inlineStr">
         <is>
@@ -1715,6 +1837,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="32" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
@@ -1788,7 +1911,7 @@
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="23" t="inlineStr">
+      <c r="A14" s="30" t="inlineStr">
         <is>
           <t>AAPL 發布會</t>
         </is>
@@ -1800,7 +1923,7 @@
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="23" t="inlineStr">
+      <c r="A15" s="30" t="inlineStr">
         <is>
           <t>META Muse</t>
         </is>
@@ -1839,6 +1962,647 @@
   <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId2"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="31" t="inlineStr">
+        <is>
+          <t>TradingView 連結索引（本檔案出現過的所有代號）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>原地已加連結的儲存格：0 個。另有 11 個儲存格同時提及多個代號 —— Excel 不支援在單一儲存格內為部分文字加連結，故該類儲存格不在原地處理，改由本表覆蓋。點擊下方連結即可開啟該代號的 TradingView 圖表。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="32" t="inlineStr">
+        <is>
+          <t>代號</t>
+        </is>
+      </c>
+      <c r="B4" s="32" t="inlineStr">
+        <is>
+          <t>名稱</t>
+        </is>
+      </c>
+      <c r="C4" s="32" t="inlineStr">
+        <is>
+          <t>TradingView</t>
+        </is>
+      </c>
+      <c r="D4" s="32" t="inlineStr">
+        <is>
+          <t>出現位置</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="41" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="B5" s="42" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="C5" s="43" t="inlineStr">
+        <is>
+          <t>NASDAQ:AAPL</t>
+        </is>
+      </c>
+      <c r="D5" s="36" t="inlineStr">
+        <is>
+          <t>00_掃描結論!A2、00_掃描結論!A18、00_掃描結論!A31、02_今日背景與時間表!B7、02_今日背景與時間表!B16、03_限制與來源!B5 …等 7 處</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="44" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="B6" s="45" t="inlineStr">
+        <is>
+          <t>Broadcom</t>
+        </is>
+      </c>
+      <c r="C6" s="46" t="inlineStr">
+        <is>
+          <t>NASDAQ:AVGO</t>
+        </is>
+      </c>
+      <c r="D6" s="40" t="inlineStr">
+        <is>
+          <t>00_掃描結論!B12、00_掃描結論!F12、00_掃描結論!F13、00_掃描結論!A31、01_板塊資金流!D4、02_今日背景與時間表!B7</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="41" t="inlineStr">
+        <is>
+          <t>CRWV</t>
+        </is>
+      </c>
+      <c r="B7" s="42" t="inlineStr">
+        <is>
+          <t>CoreWeave</t>
+        </is>
+      </c>
+      <c r="C7" s="43" t="inlineStr">
+        <is>
+          <t>NASDAQ:CRWV</t>
+        </is>
+      </c>
+      <c r="D7" s="36" t="inlineStr">
+        <is>
+          <t>00_掃描結論!A25</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="44" t="inlineStr">
+        <is>
+          <t>CVX</t>
+        </is>
+      </c>
+      <c r="B8" s="45" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C8" s="46" t="inlineStr">
+        <is>
+          <t>NYSE:CVX</t>
+        </is>
+      </c>
+      <c r="D8" s="40" t="inlineStr">
+        <is>
+          <t>00_掃描結論!B11、00_掃描結論!A31、03_限制與來源!B3、03_限制與來源!A12</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="41" t="inlineStr">
+        <is>
+          <t>DAL</t>
+        </is>
+      </c>
+      <c r="B9" s="42" t="inlineStr">
+        <is>
+          <t>Delta Air Lines</t>
+        </is>
+      </c>
+      <c r="C9" s="43" t="inlineStr">
+        <is>
+          <t>NYSE:DAL</t>
+        </is>
+      </c>
+      <c r="D9" s="36" t="inlineStr">
+        <is>
+          <t>00_掃描結論!A22</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="44" t="inlineStr">
+        <is>
+          <t>IREN</t>
+        </is>
+      </c>
+      <c r="B10" s="45" t="inlineStr">
+        <is>
+          <t>IREN</t>
+        </is>
+      </c>
+      <c r="C10" s="46" t="inlineStr">
+        <is>
+          <t>NASDAQ:IREN</t>
+        </is>
+      </c>
+      <c r="D10" s="40" t="inlineStr">
+        <is>
+          <t>00_掃描結論!A25</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="41" t="inlineStr">
+        <is>
+          <t>IXIC</t>
+        </is>
+      </c>
+      <c r="B11" s="42" t="inlineStr">
+        <is>
+          <t>納斯達克綜合指數</t>
+        </is>
+      </c>
+      <c r="C11" s="43" t="inlineStr">
+        <is>
+          <t>NASDAQ:IXIC</t>
+        </is>
+      </c>
+      <c r="D11" s="36" t="inlineStr">
+        <is>
+          <t>00_掃描結論!D5</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="44" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="B12" s="45" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
+      <c r="C12" s="46" t="inlineStr">
+        <is>
+          <t>NASDAQ:META</t>
+        </is>
+      </c>
+      <c r="D12" s="40" t="inlineStr">
+        <is>
+          <t>00_掃描結論!A19、02_今日背景與時間表!B7、03_限制與來源!B5、03_限制與來源!A15</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="41" t="inlineStr">
+        <is>
+          <t>MU</t>
+        </is>
+      </c>
+      <c r="B13" s="42" t="inlineStr">
+        <is>
+          <t>Micron</t>
+        </is>
+      </c>
+      <c r="C13" s="43" t="inlineStr">
+        <is>
+          <t>NASDAQ:MU</t>
+        </is>
+      </c>
+      <c r="D13" s="36" t="inlineStr">
+        <is>
+          <t>00_掃描結論!A25</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="44" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="B14" s="45" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="C14" s="46" t="inlineStr">
+        <is>
+          <t>NASDAQ:NVDA</t>
+        </is>
+      </c>
+      <c r="D14" s="40" t="inlineStr">
+        <is>
+          <t>00_掃描結論!F12、00_掃描結論!B13、00_掃描結論!A31、01_板塊資金流!D4、02_今日背景與時間表!B7、03_限制與來源!B5</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="41" t="inlineStr">
+        <is>
+          <t>OXY</t>
+        </is>
+      </c>
+      <c r="B15" s="42" t="inlineStr">
+        <is>
+          <t>Occidental Petroleum</t>
+        </is>
+      </c>
+      <c r="C15" s="43" t="inlineStr">
+        <is>
+          <t>NYSE:OXY</t>
+        </is>
+      </c>
+      <c r="D15" s="36" t="inlineStr">
+        <is>
+          <t>00_掃描結論!A21</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="44" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="B16" s="45" t="inlineStr">
+        <is>
+          <t>Palantir</t>
+        </is>
+      </c>
+      <c r="C16" s="46" t="inlineStr">
+        <is>
+          <t>NASDAQ:PLTR</t>
+        </is>
+      </c>
+      <c r="D16" s="40" t="inlineStr">
+        <is>
+          <t>00_掃描結論!A25</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="41" t="inlineStr">
+        <is>
+          <t>QCOM</t>
+        </is>
+      </c>
+      <c r="B17" s="42" t="inlineStr">
+        <is>
+          <t>Qualcomm</t>
+        </is>
+      </c>
+      <c r="C17" s="43" t="inlineStr">
+        <is>
+          <t>NASDAQ:QCOM</t>
+        </is>
+      </c>
+      <c r="D17" s="36" t="inlineStr">
+        <is>
+          <t>03_限制與來源!B5</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="44" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="B18" s="45" t="inlineStr">
+        <is>
+          <t>SLB (Schlumberger)</t>
+        </is>
+      </c>
+      <c r="C18" s="46" t="inlineStr">
+        <is>
+          <t>NYSE:SLB</t>
+        </is>
+      </c>
+      <c r="D18" s="40" t="inlineStr">
+        <is>
+          <t>00_掃描結論!A21</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="41" t="inlineStr">
+        <is>
+          <t>SMH</t>
+        </is>
+      </c>
+      <c r="B19" s="42" t="inlineStr">
+        <is>
+          <t>VanEck 半導體 ETF</t>
+        </is>
+      </c>
+      <c r="C19" s="43" t="inlineStr">
+        <is>
+          <t>NASDAQ:SMH</t>
+        </is>
+      </c>
+      <c r="D19" s="36" t="inlineStr">
+        <is>
+          <t>00_掃描結論!F6、00_掃描結論!C12、00_掃描結論!F12、00_掃描結論!C13、01_板塊資金流!A4、03_限制與來源!B5 …等 7 處</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="44" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B20" s="45" t="inlineStr">
+        <is>
+          <t>Tesla</t>
+        </is>
+      </c>
+      <c r="C20" s="46" t="inlineStr">
+        <is>
+          <t>NASDAQ:TSLA</t>
+        </is>
+      </c>
+      <c r="D20" s="40" t="inlineStr">
+        <is>
+          <t>00_掃描結論!A25</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="41" t="inlineStr">
+        <is>
+          <t>VLO</t>
+        </is>
+      </c>
+      <c r="B21" s="42" t="inlineStr">
+        <is>
+          <t>Valero Energy</t>
+        </is>
+      </c>
+      <c r="C21" s="43" t="inlineStr">
+        <is>
+          <t>NYSE:VLO</t>
+        </is>
+      </c>
+      <c r="D21" s="36" t="inlineStr">
+        <is>
+          <t>00_掃描結論!A20</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="44" t="inlineStr">
+        <is>
+          <t>XLE</t>
+        </is>
+      </c>
+      <c r="B22" s="45" t="inlineStr">
+        <is>
+          <t>能源類股 ETF</t>
+        </is>
+      </c>
+      <c r="C22" s="46" t="inlineStr">
+        <is>
+          <t>AMEX:XLE</t>
+        </is>
+      </c>
+      <c r="D22" s="40" t="inlineStr">
+        <is>
+          <t>00_掃描結論!F6、00_掃描結論!F10、01_板塊資金流!A5、03_限制與來源!B5、03_限制與來源!A10</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="41" t="inlineStr">
+        <is>
+          <t>XLF</t>
+        </is>
+      </c>
+      <c r="B23" s="42" t="inlineStr">
+        <is>
+          <t>金融類股 ETF</t>
+        </is>
+      </c>
+      <c r="C23" s="43" t="inlineStr">
+        <is>
+          <t>AMEX:XLF</t>
+        </is>
+      </c>
+      <c r="D23" s="36" t="inlineStr">
+        <is>
+          <t>00_掃描結論!F6、00_掃描結論!A24、01_板塊資金流!A8、03_限制與來源!A10</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="44" t="inlineStr">
+        <is>
+          <t>XLU</t>
+        </is>
+      </c>
+      <c r="B24" s="45" t="inlineStr">
+        <is>
+          <t>公用事業 ETF</t>
+        </is>
+      </c>
+      <c r="C24" s="46" t="inlineStr">
+        <is>
+          <t>AMEX:XLU</t>
+        </is>
+      </c>
+      <c r="D24" s="40" t="inlineStr">
+        <is>
+          <t>00_掃描結論!F6、00_掃描結論!B14、01_板塊資金流!A6、03_限制與來源!A10</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="41" t="inlineStr">
+        <is>
+          <t>XLV</t>
+        </is>
+      </c>
+      <c r="B25" s="42" t="inlineStr">
+        <is>
+          <t>醫療保健 ETF</t>
+        </is>
+      </c>
+      <c r="C25" s="43" t="inlineStr">
+        <is>
+          <t>AMEX:XLV</t>
+        </is>
+      </c>
+      <c r="D25" s="36" t="inlineStr">
+        <is>
+          <t>00_掃描結論!F6、00_掃描結論!A23、01_板塊資金流!A7、03_限制與來源!A10</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="44" t="inlineStr">
+        <is>
+          <t>XOM</t>
+        </is>
+      </c>
+      <c r="B26" s="45" t="inlineStr">
+        <is>
+          <t>ExxonMobil</t>
+        </is>
+      </c>
+      <c r="C26" s="46" t="inlineStr">
+        <is>
+          <t>NYSE:XOM</t>
+        </is>
+      </c>
+      <c r="D26" s="40" t="inlineStr">
+        <is>
+          <t>00_掃描結論!B10、00_掃描結論!F11、00_掃描結論!F21、00_掃描結論!A31、03_限制與來源!B3、03_限制與來源!B5 …等 7 處</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="41" t="inlineStr">
+        <is>
+          <t>DJI</t>
+        </is>
+      </c>
+      <c r="B27" s="42" t="inlineStr">
+        <is>
+          <t>道瓊工業指數</t>
+        </is>
+      </c>
+      <c r="C27" s="43" t="inlineStr">
+        <is>
+          <t>DJ:DJI</t>
+        </is>
+      </c>
+      <c r="D27" s="36" t="inlineStr">
+        <is>
+          <t>00_掃描結論!C5</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="44" t="inlineStr">
+        <is>
+          <t>RUT</t>
+        </is>
+      </c>
+      <c r="B28" s="45" t="inlineStr">
+        <is>
+          <t>羅素 2000 指數</t>
+        </is>
+      </c>
+      <c r="C28" s="46" t="inlineStr">
+        <is>
+          <t>TVC:RUT</t>
+        </is>
+      </c>
+      <c r="D28" s="40" t="inlineStr">
+        <is>
+          <t>00_掃描結論!E5</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="41" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="B29" s="42" t="inlineStr">
+        <is>
+          <t>標普 500 指數</t>
+        </is>
+      </c>
+      <c r="C29" s="43" t="inlineStr">
+        <is>
+          <t>SP:SPX</t>
+        </is>
+      </c>
+      <c r="D29" s="36" t="inlineStr">
+        <is>
+          <t>00_掃描結論!B5</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId25"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/2026-09-09_盤中掃描_低波幅20分鐘均線.xlsx
+++ b/output/2026-09-09_盤中掃描_低波幅20分鐘均線.xlsx
@@ -223,7 +223,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -340,6 +340,24 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -1437,7 +1455,7 @@
       </c>
     </row>
     <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="35" t="inlineStr">
+      <c r="A4" s="43" t="inlineStr">
         <is>
           <t>SMH 半導體</t>
         </is>
@@ -1457,7 +1475,7 @@
       </c>
     </row>
     <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="35" t="inlineStr">
+      <c r="A5" s="43" t="inlineStr">
         <is>
           <t>XLE 能源</t>
         </is>
@@ -1477,7 +1495,7 @@
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="35" t="inlineStr">
+      <c r="A6" s="43" t="inlineStr">
         <is>
           <t>XLU 公用</t>
         </is>
@@ -1497,7 +1515,7 @@
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="35" t="inlineStr">
+      <c r="A7" s="43" t="inlineStr">
         <is>
           <t>XLV 醫療</t>
         </is>
@@ -1517,7 +1535,7 @@
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="35" t="inlineStr">
+      <c r="A8" s="43" t="inlineStr">
         <is>
           <t>XLF 金融</t>
         </is>
@@ -1668,7 +1686,7 @@
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="33" t="inlineStr">
+      <c r="A12" s="41" t="inlineStr">
         <is>
           <t>11:12</t>
         </is>
@@ -1680,7 +1698,7 @@
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="33" t="inlineStr">
+      <c r="A13" s="41" t="inlineStr">
         <is>
           <t>11:30–13:00</t>
         </is>
@@ -1692,7 +1710,7 @@
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="33" t="inlineStr">
+      <c r="A14" s="41" t="inlineStr">
         <is>
           <t>13:00</t>
         </is>
@@ -1704,7 +1722,7 @@
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="33" t="inlineStr">
+      <c r="A15" s="41" t="inlineStr">
         <is>
           <t>13:05–14:00</t>
         </is>
@@ -1716,7 +1734,7 @@
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="33" t="inlineStr">
+      <c r="A16" s="41" t="inlineStr">
         <is>
           <t>約 13:00 起</t>
         </is>
@@ -1728,7 +1746,7 @@
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="33" t="inlineStr">
+      <c r="A17" s="41" t="inlineStr">
         <is>
           <t>15:00–16:00</t>
         </is>
@@ -1740,7 +1758,7 @@
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="33" t="inlineStr">
+      <c r="A18" s="41" t="inlineStr">
         <is>
           <t>盤後 / 隔夜</t>
         </is>
@@ -2022,17 +2040,17 @@
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="41" t="inlineStr">
+      <c r="A5" s="47" t="inlineStr">
         <is>
           <t>AAPL</t>
         </is>
       </c>
-      <c r="B5" s="42" t="inlineStr">
+      <c r="B5" s="48" t="inlineStr">
         <is>
           <t>Apple</t>
         </is>
       </c>
-      <c r="C5" s="43" t="inlineStr">
+      <c r="C5" s="49" t="inlineStr">
         <is>
           <t>NASDAQ:AAPL</t>
         </is>
@@ -2044,17 +2062,17 @@
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="44" t="inlineStr">
+      <c r="A6" s="50" t="inlineStr">
         <is>
           <t>AVGO</t>
         </is>
       </c>
-      <c r="B6" s="45" t="inlineStr">
+      <c r="B6" s="51" t="inlineStr">
         <is>
           <t>Broadcom</t>
         </is>
       </c>
-      <c r="C6" s="46" t="inlineStr">
+      <c r="C6" s="52" t="inlineStr">
         <is>
           <t>NASDAQ:AVGO</t>
         </is>
@@ -2066,17 +2084,17 @@
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="41" t="inlineStr">
+      <c r="A7" s="47" t="inlineStr">
         <is>
           <t>CRWV</t>
         </is>
       </c>
-      <c r="B7" s="42" t="inlineStr">
+      <c r="B7" s="48" t="inlineStr">
         <is>
           <t>CoreWeave</t>
         </is>
       </c>
-      <c r="C7" s="43" t="inlineStr">
+      <c r="C7" s="49" t="inlineStr">
         <is>
           <t>NASDAQ:CRWV</t>
         </is>
@@ -2088,17 +2106,17 @@
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="44" t="inlineStr">
+      <c r="A8" s="50" t="inlineStr">
         <is>
           <t>CVX</t>
         </is>
       </c>
-      <c r="B8" s="45" t="inlineStr">
+      <c r="B8" s="51" t="inlineStr">
         <is>
           <t>Chevron</t>
         </is>
       </c>
-      <c r="C8" s="46" t="inlineStr">
+      <c r="C8" s="52" t="inlineStr">
         <is>
           <t>NYSE:CVX</t>
         </is>
@@ -2110,17 +2128,17 @@
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="41" t="inlineStr">
+      <c r="A9" s="47" t="inlineStr">
         <is>
           <t>DAL</t>
         </is>
       </c>
-      <c r="B9" s="42" t="inlineStr">
+      <c r="B9" s="48" t="inlineStr">
         <is>
           <t>Delta Air Lines</t>
         </is>
       </c>
-      <c r="C9" s="43" t="inlineStr">
+      <c r="C9" s="49" t="inlineStr">
         <is>
           <t>NYSE:DAL</t>
         </is>
@@ -2132,17 +2150,17 @@
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="44" t="inlineStr">
+      <c r="A10" s="50" t="inlineStr">
         <is>
           <t>IREN</t>
         </is>
       </c>
-      <c r="B10" s="45" t="inlineStr">
+      <c r="B10" s="51" t="inlineStr">
         <is>
           <t>IREN</t>
         </is>
       </c>
-      <c r="C10" s="46" t="inlineStr">
+      <c r="C10" s="52" t="inlineStr">
         <is>
           <t>NASDAQ:IREN</t>
         </is>
@@ -2154,17 +2172,17 @@
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="41" t="inlineStr">
+      <c r="A11" s="47" t="inlineStr">
         <is>
           <t>IXIC</t>
         </is>
       </c>
-      <c r="B11" s="42" t="inlineStr">
+      <c r="B11" s="48" t="inlineStr">
         <is>
           <t>納斯達克綜合指數</t>
         </is>
       </c>
-      <c r="C11" s="43" t="inlineStr">
+      <c r="C11" s="49" t="inlineStr">
         <is>
           <t>NASDAQ:IXIC</t>
         </is>
@@ -2176,17 +2194,17 @@
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="44" t="inlineStr">
+      <c r="A12" s="50" t="inlineStr">
         <is>
           <t>META</t>
         </is>
       </c>
-      <c r="B12" s="45" t="inlineStr">
+      <c r="B12" s="51" t="inlineStr">
         <is>
           <t>Meta Platforms</t>
         </is>
       </c>
-      <c r="C12" s="46" t="inlineStr">
+      <c r="C12" s="52" t="inlineStr">
         <is>
           <t>NASDAQ:META</t>
         </is>
@@ -2198,17 +2216,17 @@
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="41" t="inlineStr">
+      <c r="A13" s="47" t="inlineStr">
         <is>
           <t>MU</t>
         </is>
       </c>
-      <c r="B13" s="42" t="inlineStr">
+      <c r="B13" s="48" t="inlineStr">
         <is>
           <t>Micron</t>
         </is>
       </c>
-      <c r="C13" s="43" t="inlineStr">
+      <c r="C13" s="49" t="inlineStr">
         <is>
           <t>NASDAQ:MU</t>
         </is>
@@ -2220,17 +2238,17 @@
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="44" t="inlineStr">
+      <c r="A14" s="50" t="inlineStr">
         <is>
           <t>NVDA</t>
         </is>
       </c>
-      <c r="B14" s="45" t="inlineStr">
+      <c r="B14" s="51" t="inlineStr">
         <is>
           <t>NVIDIA</t>
         </is>
       </c>
-      <c r="C14" s="46" t="inlineStr">
+      <c r="C14" s="52" t="inlineStr">
         <is>
           <t>NASDAQ:NVDA</t>
         </is>
@@ -2242,17 +2260,17 @@
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="41" t="inlineStr">
+      <c r="A15" s="47" t="inlineStr">
         <is>
           <t>OXY</t>
         </is>
       </c>
-      <c r="B15" s="42" t="inlineStr">
+      <c r="B15" s="48" t="inlineStr">
         <is>
           <t>Occidental Petroleum</t>
         </is>
       </c>
-      <c r="C15" s="43" t="inlineStr">
+      <c r="C15" s="49" t="inlineStr">
         <is>
           <t>NYSE:OXY</t>
         </is>
@@ -2264,17 +2282,17 @@
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="44" t="inlineStr">
+      <c r="A16" s="50" t="inlineStr">
         <is>
           <t>PLTR</t>
         </is>
       </c>
-      <c r="B16" s="45" t="inlineStr">
+      <c r="B16" s="51" t="inlineStr">
         <is>
           <t>Palantir</t>
         </is>
       </c>
-      <c r="C16" s="46" t="inlineStr">
+      <c r="C16" s="52" t="inlineStr">
         <is>
           <t>NASDAQ:PLTR</t>
         </is>
@@ -2286,17 +2304,17 @@
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="41" t="inlineStr">
+      <c r="A17" s="47" t="inlineStr">
         <is>
           <t>QCOM</t>
         </is>
       </c>
-      <c r="B17" s="42" t="inlineStr">
+      <c r="B17" s="48" t="inlineStr">
         <is>
           <t>Qualcomm</t>
         </is>
       </c>
-      <c r="C17" s="43" t="inlineStr">
+      <c r="C17" s="49" t="inlineStr">
         <is>
           <t>NASDAQ:QCOM</t>
         </is>
@@ -2308,17 +2326,17 @@
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="44" t="inlineStr">
+      <c r="A18" s="50" t="inlineStr">
         <is>
           <t>SLB</t>
         </is>
       </c>
-      <c r="B18" s="45" t="inlineStr">
+      <c r="B18" s="51" t="inlineStr">
         <is>
           <t>SLB (Schlumberger)</t>
         </is>
       </c>
-      <c r="C18" s="46" t="inlineStr">
+      <c r="C18" s="52" t="inlineStr">
         <is>
           <t>NYSE:SLB</t>
         </is>
@@ -2330,17 +2348,17 @@
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="41" t="inlineStr">
+      <c r="A19" s="47" t="inlineStr">
         <is>
           <t>SMH</t>
         </is>
       </c>
-      <c r="B19" s="42" t="inlineStr">
+      <c r="B19" s="48" t="inlineStr">
         <is>
           <t>VanEck 半導體 ETF</t>
         </is>
       </c>
-      <c r="C19" s="43" t="inlineStr">
+      <c r="C19" s="49" t="inlineStr">
         <is>
           <t>NASDAQ:SMH</t>
         </is>
@@ -2352,17 +2370,17 @@
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="44" t="inlineStr">
+      <c r="A20" s="50" t="inlineStr">
         <is>
           <t>TSLA</t>
         </is>
       </c>
-      <c r="B20" s="45" t="inlineStr">
+      <c r="B20" s="51" t="inlineStr">
         <is>
           <t>Tesla</t>
         </is>
       </c>
-      <c r="C20" s="46" t="inlineStr">
+      <c r="C20" s="52" t="inlineStr">
         <is>
           <t>NASDAQ:TSLA</t>
         </is>
@@ -2374,17 +2392,17 @@
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="41" t="inlineStr">
+      <c r="A21" s="47" t="inlineStr">
         <is>
           <t>VLO</t>
         </is>
       </c>
-      <c r="B21" s="42" t="inlineStr">
+      <c r="B21" s="48" t="inlineStr">
         <is>
           <t>Valero Energy</t>
         </is>
       </c>
-      <c r="C21" s="43" t="inlineStr">
+      <c r="C21" s="49" t="inlineStr">
         <is>
           <t>NYSE:VLO</t>
         </is>
@@ -2396,17 +2414,17 @@
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="44" t="inlineStr">
+      <c r="A22" s="50" t="inlineStr">
         <is>
           <t>XLE</t>
         </is>
       </c>
-      <c r="B22" s="45" t="inlineStr">
+      <c r="B22" s="51" t="inlineStr">
         <is>
           <t>能源類股 ETF</t>
         </is>
       </c>
-      <c r="C22" s="46" t="inlineStr">
+      <c r="C22" s="52" t="inlineStr">
         <is>
           <t>AMEX:XLE</t>
         </is>
@@ -2418,17 +2436,17 @@
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="41" t="inlineStr">
+      <c r="A23" s="47" t="inlineStr">
         <is>
           <t>XLF</t>
         </is>
       </c>
-      <c r="B23" s="42" t="inlineStr">
+      <c r="B23" s="48" t="inlineStr">
         <is>
           <t>金融類股 ETF</t>
         </is>
       </c>
-      <c r="C23" s="43" t="inlineStr">
+      <c r="C23" s="49" t="inlineStr">
         <is>
           <t>AMEX:XLF</t>
         </is>
@@ -2440,17 +2458,17 @@
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="44" t="inlineStr">
+      <c r="A24" s="50" t="inlineStr">
         <is>
           <t>XLU</t>
         </is>
       </c>
-      <c r="B24" s="45" t="inlineStr">
+      <c r="B24" s="51" t="inlineStr">
         <is>
           <t>公用事業 ETF</t>
         </is>
       </c>
-      <c r="C24" s="46" t="inlineStr">
+      <c r="C24" s="52" t="inlineStr">
         <is>
           <t>AMEX:XLU</t>
         </is>
@@ -2462,17 +2480,17 @@
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="41" t="inlineStr">
+      <c r="A25" s="47" t="inlineStr">
         <is>
           <t>XLV</t>
         </is>
       </c>
-      <c r="B25" s="42" t="inlineStr">
+      <c r="B25" s="48" t="inlineStr">
         <is>
           <t>醫療保健 ETF</t>
         </is>
       </c>
-      <c r="C25" s="43" t="inlineStr">
+      <c r="C25" s="49" t="inlineStr">
         <is>
           <t>AMEX:XLV</t>
         </is>
@@ -2484,17 +2502,17 @@
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="44" t="inlineStr">
+      <c r="A26" s="50" t="inlineStr">
         <is>
           <t>XOM</t>
         </is>
       </c>
-      <c r="B26" s="45" t="inlineStr">
+      <c r="B26" s="51" t="inlineStr">
         <is>
           <t>ExxonMobil</t>
         </is>
       </c>
-      <c r="C26" s="46" t="inlineStr">
+      <c r="C26" s="52" t="inlineStr">
         <is>
           <t>NYSE:XOM</t>
         </is>
@@ -2506,17 +2524,17 @@
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="41" t="inlineStr">
+      <c r="A27" s="47" t="inlineStr">
         <is>
           <t>DJI</t>
         </is>
       </c>
-      <c r="B27" s="42" t="inlineStr">
+      <c r="B27" s="48" t="inlineStr">
         <is>
           <t>道瓊工業指數</t>
         </is>
       </c>
-      <c r="C27" s="43" t="inlineStr">
+      <c r="C27" s="49" t="inlineStr">
         <is>
           <t>DJ:DJI</t>
         </is>
@@ -2528,17 +2546,17 @@
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="44" t="inlineStr">
+      <c r="A28" s="50" t="inlineStr">
         <is>
           <t>RUT</t>
         </is>
       </c>
-      <c r="B28" s="45" t="inlineStr">
+      <c r="B28" s="51" t="inlineStr">
         <is>
           <t>羅素 2000 指數</t>
         </is>
       </c>
-      <c r="C28" s="46" t="inlineStr">
+      <c r="C28" s="52" t="inlineStr">
         <is>
           <t>TVC:RUT</t>
         </is>
@@ -2550,17 +2568,17 @@
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="41" t="inlineStr">
+      <c r="A29" s="47" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="B29" s="42" t="inlineStr">
+      <c r="B29" s="48" t="inlineStr">
         <is>
           <t>標普 500 指數</t>
         </is>
       </c>
-      <c r="C29" s="43" t="inlineStr">
+      <c r="C29" s="49" t="inlineStr">
         <is>
           <t>SP:SPX</t>
         </is>

--- a/output/2026-09-09_盤中掃描_低波幅20分鐘均線.xlsx
+++ b/output/2026-09-09_盤中掃描_低波幅20分鐘均線.xlsx
@@ -223,7 +223,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -340,6 +340,60 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -1455,7 +1509,7 @@
       </c>
     </row>
     <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="43" t="inlineStr">
+      <c r="A4" s="61" t="inlineStr">
         <is>
           <t>SMH 半導體</t>
         </is>
@@ -1475,7 +1529,7 @@
       </c>
     </row>
     <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="43" t="inlineStr">
+      <c r="A5" s="61" t="inlineStr">
         <is>
           <t>XLE 能源</t>
         </is>
@@ -1495,7 +1549,7 @@
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="43" t="inlineStr">
+      <c r="A6" s="61" t="inlineStr">
         <is>
           <t>XLU 公用</t>
         </is>
@@ -1515,7 +1569,7 @@
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="43" t="inlineStr">
+      <c r="A7" s="61" t="inlineStr">
         <is>
           <t>XLV 醫療</t>
         </is>
@@ -1535,7 +1589,7 @@
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="43" t="inlineStr">
+      <c r="A8" s="61" t="inlineStr">
         <is>
           <t>XLF 金融</t>
         </is>
@@ -1686,7 +1740,7 @@
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="41" t="inlineStr">
+      <c r="A12" s="59" t="inlineStr">
         <is>
           <t>11:12</t>
         </is>
@@ -1698,7 +1752,7 @@
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="41" t="inlineStr">
+      <c r="A13" s="59" t="inlineStr">
         <is>
           <t>11:30–13:00</t>
         </is>
@@ -1710,7 +1764,7 @@
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="41" t="inlineStr">
+      <c r="A14" s="59" t="inlineStr">
         <is>
           <t>13:00</t>
         </is>
@@ -1722,7 +1776,7 @@
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="41" t="inlineStr">
+      <c r="A15" s="59" t="inlineStr">
         <is>
           <t>13:05–14:00</t>
         </is>
@@ -1734,7 +1788,7 @@
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="41" t="inlineStr">
+      <c r="A16" s="59" t="inlineStr">
         <is>
           <t>約 13:00 起</t>
         </is>
@@ -1746,7 +1800,7 @@
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="41" t="inlineStr">
+      <c r="A17" s="59" t="inlineStr">
         <is>
           <t>15:00–16:00</t>
         </is>
@@ -1758,7 +1812,7 @@
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="41" t="inlineStr">
+      <c r="A18" s="59" t="inlineStr">
         <is>
           <t>盤後 / 隔夜</t>
         </is>
@@ -2040,17 +2094,17 @@
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="47" t="inlineStr">
+      <c r="A5" s="65" t="inlineStr">
         <is>
           <t>AAPL</t>
         </is>
       </c>
-      <c r="B5" s="48" t="inlineStr">
+      <c r="B5" s="66" t="inlineStr">
         <is>
           <t>Apple</t>
         </is>
       </c>
-      <c r="C5" s="49" t="inlineStr">
+      <c r="C5" s="67" t="inlineStr">
         <is>
           <t>NASDAQ:AAPL</t>
         </is>
@@ -2062,17 +2116,17 @@
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="50" t="inlineStr">
+      <c r="A6" s="68" t="inlineStr">
         <is>
           <t>AVGO</t>
         </is>
       </c>
-      <c r="B6" s="51" t="inlineStr">
+      <c r="B6" s="69" t="inlineStr">
         <is>
           <t>Broadcom</t>
         </is>
       </c>
-      <c r="C6" s="52" t="inlineStr">
+      <c r="C6" s="70" t="inlineStr">
         <is>
           <t>NASDAQ:AVGO</t>
         </is>
@@ -2084,17 +2138,17 @@
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="47" t="inlineStr">
+      <c r="A7" s="65" t="inlineStr">
         <is>
           <t>CRWV</t>
         </is>
       </c>
-      <c r="B7" s="48" t="inlineStr">
+      <c r="B7" s="66" t="inlineStr">
         <is>
           <t>CoreWeave</t>
         </is>
       </c>
-      <c r="C7" s="49" t="inlineStr">
+      <c r="C7" s="67" t="inlineStr">
         <is>
           <t>NASDAQ:CRWV</t>
         </is>
@@ -2106,17 +2160,17 @@
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="50" t="inlineStr">
+      <c r="A8" s="68" t="inlineStr">
         <is>
           <t>CVX</t>
         </is>
       </c>
-      <c r="B8" s="51" t="inlineStr">
+      <c r="B8" s="69" t="inlineStr">
         <is>
           <t>Chevron</t>
         </is>
       </c>
-      <c r="C8" s="52" t="inlineStr">
+      <c r="C8" s="70" t="inlineStr">
         <is>
           <t>NYSE:CVX</t>
         </is>
@@ -2128,17 +2182,17 @@
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="47" t="inlineStr">
+      <c r="A9" s="65" t="inlineStr">
         <is>
           <t>DAL</t>
         </is>
       </c>
-      <c r="B9" s="48" t="inlineStr">
+      <c r="B9" s="66" t="inlineStr">
         <is>
           <t>Delta Air Lines</t>
         </is>
       </c>
-      <c r="C9" s="49" t="inlineStr">
+      <c r="C9" s="67" t="inlineStr">
         <is>
           <t>NYSE:DAL</t>
         </is>
@@ -2150,17 +2204,17 @@
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="50" t="inlineStr">
+      <c r="A10" s="68" t="inlineStr">
         <is>
           <t>IREN</t>
         </is>
       </c>
-      <c r="B10" s="51" t="inlineStr">
+      <c r="B10" s="69" t="inlineStr">
         <is>
           <t>IREN</t>
         </is>
       </c>
-      <c r="C10" s="52" t="inlineStr">
+      <c r="C10" s="70" t="inlineStr">
         <is>
           <t>NASDAQ:IREN</t>
         </is>
@@ -2172,17 +2226,17 @@
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="47" t="inlineStr">
+      <c r="A11" s="65" t="inlineStr">
         <is>
           <t>IXIC</t>
         </is>
       </c>
-      <c r="B11" s="48" t="inlineStr">
+      <c r="B11" s="66" t="inlineStr">
         <is>
           <t>納斯達克綜合指數</t>
         </is>
       </c>
-      <c r="C11" s="49" t="inlineStr">
+      <c r="C11" s="67" t="inlineStr">
         <is>
           <t>NASDAQ:IXIC</t>
         </is>
@@ -2194,17 +2248,17 @@
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="50" t="inlineStr">
+      <c r="A12" s="68" t="inlineStr">
         <is>
           <t>META</t>
         </is>
       </c>
-      <c r="B12" s="51" t="inlineStr">
+      <c r="B12" s="69" t="inlineStr">
         <is>
           <t>Meta Platforms</t>
         </is>
       </c>
-      <c r="C12" s="52" t="inlineStr">
+      <c r="C12" s="70" t="inlineStr">
         <is>
           <t>NASDAQ:META</t>
         </is>
@@ -2216,17 +2270,17 @@
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="47" t="inlineStr">
+      <c r="A13" s="65" t="inlineStr">
         <is>
           <t>MU</t>
         </is>
       </c>
-      <c r="B13" s="48" t="inlineStr">
+      <c r="B13" s="66" t="inlineStr">
         <is>
           <t>Micron</t>
         </is>
       </c>
-      <c r="C13" s="49" t="inlineStr">
+      <c r="C13" s="67" t="inlineStr">
         <is>
           <t>NASDAQ:MU</t>
         </is>
@@ -2238,17 +2292,17 @@
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="50" t="inlineStr">
+      <c r="A14" s="68" t="inlineStr">
         <is>
           <t>NVDA</t>
         </is>
       </c>
-      <c r="B14" s="51" t="inlineStr">
+      <c r="B14" s="69" t="inlineStr">
         <is>
           <t>NVIDIA</t>
         </is>
       </c>
-      <c r="C14" s="52" t="inlineStr">
+      <c r="C14" s="70" t="inlineStr">
         <is>
           <t>NASDAQ:NVDA</t>
         </is>
@@ -2260,17 +2314,17 @@
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="47" t="inlineStr">
+      <c r="A15" s="65" t="inlineStr">
         <is>
           <t>OXY</t>
         </is>
       </c>
-      <c r="B15" s="48" t="inlineStr">
+      <c r="B15" s="66" t="inlineStr">
         <is>
           <t>Occidental Petroleum</t>
         </is>
       </c>
-      <c r="C15" s="49" t="inlineStr">
+      <c r="C15" s="67" t="inlineStr">
         <is>
           <t>NYSE:OXY</t>
         </is>
@@ -2282,17 +2336,17 @@
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="50" t="inlineStr">
+      <c r="A16" s="68" t="inlineStr">
         <is>
           <t>PLTR</t>
         </is>
       </c>
-      <c r="B16" s="51" t="inlineStr">
+      <c r="B16" s="69" t="inlineStr">
         <is>
           <t>Palantir</t>
         </is>
       </c>
-      <c r="C16" s="52" t="inlineStr">
+      <c r="C16" s="70" t="inlineStr">
         <is>
           <t>NASDAQ:PLTR</t>
         </is>
@@ -2304,17 +2358,17 @@
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="47" t="inlineStr">
+      <c r="A17" s="65" t="inlineStr">
         <is>
           <t>QCOM</t>
         </is>
       </c>
-      <c r="B17" s="48" t="inlineStr">
+      <c r="B17" s="66" t="inlineStr">
         <is>
           <t>Qualcomm</t>
         </is>
       </c>
-      <c r="C17" s="49" t="inlineStr">
+      <c r="C17" s="67" t="inlineStr">
         <is>
           <t>NASDAQ:QCOM</t>
         </is>
@@ -2326,17 +2380,17 @@
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="50" t="inlineStr">
+      <c r="A18" s="68" t="inlineStr">
         <is>
           <t>SLB</t>
         </is>
       </c>
-      <c r="B18" s="51" t="inlineStr">
+      <c r="B18" s="69" t="inlineStr">
         <is>
           <t>SLB (Schlumberger)</t>
         </is>
       </c>
-      <c r="C18" s="52" t="inlineStr">
+      <c r="C18" s="70" t="inlineStr">
         <is>
           <t>NYSE:SLB</t>
         </is>
@@ -2348,17 +2402,17 @@
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="47" t="inlineStr">
+      <c r="A19" s="65" t="inlineStr">
         <is>
           <t>SMH</t>
         </is>
       </c>
-      <c r="B19" s="48" t="inlineStr">
+      <c r="B19" s="66" t="inlineStr">
         <is>
           <t>VanEck 半導體 ETF</t>
         </is>
       </c>
-      <c r="C19" s="49" t="inlineStr">
+      <c r="C19" s="67" t="inlineStr">
         <is>
           <t>NASDAQ:SMH</t>
         </is>
@@ -2370,17 +2424,17 @@
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="50" t="inlineStr">
+      <c r="A20" s="68" t="inlineStr">
         <is>
           <t>TSLA</t>
         </is>
       </c>
-      <c r="B20" s="51" t="inlineStr">
+      <c r="B20" s="69" t="inlineStr">
         <is>
           <t>Tesla</t>
         </is>
       </c>
-      <c r="C20" s="52" t="inlineStr">
+      <c r="C20" s="70" t="inlineStr">
         <is>
           <t>NASDAQ:TSLA</t>
         </is>
@@ -2392,17 +2446,17 @@
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="47" t="inlineStr">
+      <c r="A21" s="65" t="inlineStr">
         <is>
           <t>VLO</t>
         </is>
       </c>
-      <c r="B21" s="48" t="inlineStr">
+      <c r="B21" s="66" t="inlineStr">
         <is>
           <t>Valero Energy</t>
         </is>
       </c>
-      <c r="C21" s="49" t="inlineStr">
+      <c r="C21" s="67" t="inlineStr">
         <is>
           <t>NYSE:VLO</t>
         </is>
@@ -2414,17 +2468,17 @@
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="50" t="inlineStr">
+      <c r="A22" s="68" t="inlineStr">
         <is>
           <t>XLE</t>
         </is>
       </c>
-      <c r="B22" s="51" t="inlineStr">
+      <c r="B22" s="69" t="inlineStr">
         <is>
           <t>能源類股 ETF</t>
         </is>
       </c>
-      <c r="C22" s="52" t="inlineStr">
+      <c r="C22" s="70" t="inlineStr">
         <is>
           <t>AMEX:XLE</t>
         </is>
@@ -2436,17 +2490,17 @@
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="47" t="inlineStr">
+      <c r="A23" s="65" t="inlineStr">
         <is>
           <t>XLF</t>
         </is>
       </c>
-      <c r="B23" s="48" t="inlineStr">
+      <c r="B23" s="66" t="inlineStr">
         <is>
           <t>金融類股 ETF</t>
         </is>
       </c>
-      <c r="C23" s="49" t="inlineStr">
+      <c r="C23" s="67" t="inlineStr">
         <is>
           <t>AMEX:XLF</t>
         </is>
@@ -2458,17 +2512,17 @@
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="50" t="inlineStr">
+      <c r="A24" s="68" t="inlineStr">
         <is>
           <t>XLU</t>
         </is>
       </c>
-      <c r="B24" s="51" t="inlineStr">
+      <c r="B24" s="69" t="inlineStr">
         <is>
           <t>公用事業 ETF</t>
         </is>
       </c>
-      <c r="C24" s="52" t="inlineStr">
+      <c r="C24" s="70" t="inlineStr">
         <is>
           <t>AMEX:XLU</t>
         </is>
@@ -2480,17 +2534,17 @@
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="47" t="inlineStr">
+      <c r="A25" s="65" t="inlineStr">
         <is>
           <t>XLV</t>
         </is>
       </c>
-      <c r="B25" s="48" t="inlineStr">
+      <c r="B25" s="66" t="inlineStr">
         <is>
           <t>醫療保健 ETF</t>
         </is>
       </c>
-      <c r="C25" s="49" t="inlineStr">
+      <c r="C25" s="67" t="inlineStr">
         <is>
           <t>AMEX:XLV</t>
         </is>
@@ -2502,17 +2556,17 @@
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="50" t="inlineStr">
+      <c r="A26" s="68" t="inlineStr">
         <is>
           <t>XOM</t>
         </is>
       </c>
-      <c r="B26" s="51" t="inlineStr">
+      <c r="B26" s="69" t="inlineStr">
         <is>
           <t>ExxonMobil</t>
         </is>
       </c>
-      <c r="C26" s="52" t="inlineStr">
+      <c r="C26" s="70" t="inlineStr">
         <is>
           <t>NYSE:XOM</t>
         </is>
@@ -2524,17 +2578,17 @@
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="47" t="inlineStr">
+      <c r="A27" s="65" t="inlineStr">
         <is>
           <t>DJI</t>
         </is>
       </c>
-      <c r="B27" s="48" t="inlineStr">
+      <c r="B27" s="66" t="inlineStr">
         <is>
           <t>道瓊工業指數</t>
         </is>
       </c>
-      <c r="C27" s="49" t="inlineStr">
+      <c r="C27" s="67" t="inlineStr">
         <is>
           <t>DJ:DJI</t>
         </is>
@@ -2546,17 +2600,17 @@
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="50" t="inlineStr">
+      <c r="A28" s="68" t="inlineStr">
         <is>
           <t>RUT</t>
         </is>
       </c>
-      <c r="B28" s="51" t="inlineStr">
+      <c r="B28" s="69" t="inlineStr">
         <is>
           <t>羅素 2000 指數</t>
         </is>
       </c>
-      <c r="C28" s="52" t="inlineStr">
+      <c r="C28" s="70" t="inlineStr">
         <is>
           <t>TVC:RUT</t>
         </is>
@@ -2568,17 +2622,17 @@
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="47" t="inlineStr">
+      <c r="A29" s="65" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="B29" s="48" t="inlineStr">
+      <c r="B29" s="66" t="inlineStr">
         <is>
           <t>標普 500 指數</t>
         </is>
       </c>
-      <c r="C29" s="49" t="inlineStr">
+      <c r="C29" s="67" t="inlineStr">
         <is>
           <t>SP:SPX</t>
         </is>
